--- a/results/Q.xlsx
+++ b/results/Q.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\427消融实验版\SECT-a-new-method-based-on-louvain-main\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huawei\Desktop\结果\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9052332-1D03-4519-B26C-E086AE0BCCAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="860" yWindow="1210" windowWidth="10520" windowHeight="7600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,13 +24,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="17">
   <si>
     <t>tree</t>
   </si>
   <si>
     <t>lol</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>g22</t>
   </si>
   <si>
     <t>email-Eu-core</t>
@@ -88,7 +90,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -162,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -172,6 +174,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
@@ -453,21 +458,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.75" customWidth="1"/>
-    <col min="2" max="2" width="9.4140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.4140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.1640625" customWidth="1"/>
-    <col min="6" max="7" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -476,44 +480,44 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1">
-        <v>0.85012100000000002</v>
+        <v>0.86150300000000002</v>
       </c>
       <c r="C2" s="1">
-        <v>0.70994800000000002</v>
+        <v>0.709758</v>
       </c>
       <c r="D2" s="1">
         <v>0.86239900000000003</v>
       </c>
       <c r="E2" s="1">
-        <v>0.79986299999999999</v>
+        <v>0.83274300000000001</v>
       </c>
       <c r="F2" s="1">
-        <v>0.92438399999999998</v>
+        <v>0.92388700000000001</v>
       </c>
       <c r="G2" s="1">
-        <v>0.93330500000000005</v>
+        <v>0.93280600000000002</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2">
         <v>0.79464999999999997</v>
@@ -522,27 +526,27 @@
         <v>0.67325599999999997</v>
       </c>
       <c r="D3" s="2">
-        <v>0.77017500000000005</v>
+        <v>0.77134800000000003</v>
       </c>
       <c r="E3" s="2">
-        <v>0.40035100000000001</v>
+        <v>0.41567300000000001</v>
       </c>
       <c r="F3" s="2">
-        <v>0.82062900000000005</v>
+        <v>0.82064099999999995</v>
       </c>
       <c r="G3" s="2">
-        <v>0.63149599999999995</v>
+        <v>0.63490000000000002</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="2">
         <v>-6.4626000000000003E-2</v>
       </c>
       <c r="C4" s="2">
-        <v>6.1224000000000001E-2</v>
+        <v>2.3557000000000002E-2</v>
       </c>
       <c r="D4" s="2">
         <v>-8.0520000000000001E-3</v>
@@ -554,15 +558,15 @@
         <v>0.104187</v>
       </c>
       <c r="G4" s="2">
-        <v>2.9146999999999999E-2</v>
+        <v>2.7876000000000001E-2</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2">
-        <v>0.80025000000000002</v>
+        <v>0.79335</v>
       </c>
       <c r="C5" s="2">
         <v>0.67325599999999997</v>
@@ -571,18 +575,18 @@
         <v>0.77134800000000003</v>
       </c>
       <c r="E5" s="2">
-        <v>0.417379</v>
+        <v>0.41733300000000001</v>
       </c>
       <c r="F5" s="2">
-        <v>0.820658</v>
+        <v>0.82042400000000004</v>
       </c>
       <c r="G5" s="2">
-        <v>0.59684599999999999</v>
+        <v>0.63752399999999998</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" s="2">
         <v>0.66805000000000003</v>
@@ -600,12 +604,12 @@
         <v>0.813226</v>
       </c>
       <c r="G6" s="2">
-        <v>0.529416</v>
+        <v>0.38718200000000003</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" s="2">
         <v>0.79090000000000005</v>
@@ -628,7 +632,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" s="2">
         <v>0.76595000000000002</v>
@@ -646,12 +650,12 @@
         <v>0.81613599999999997</v>
       </c>
       <c r="G8" s="2">
-        <v>0.52113299999999996</v>
+        <v>0.57610600000000001</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>0</v>
@@ -660,24 +664,24 @@
         <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" s="2">
-        <v>0.78574999999999995</v>
+        <v>0.75409999999999999</v>
       </c>
       <c r="C11" s="2">
         <v>0.59102900000000003</v>
@@ -686,36 +690,36 @@
         <v>0.77017500000000005</v>
       </c>
       <c r="E11" s="2">
-        <v>0.335781</v>
+        <v>0.32276500000000002</v>
       </c>
       <c r="F11" s="2">
-        <v>0.77153099999999997</v>
-      </c>
-      <c r="G11" s="4">
-        <v>0.60495299999999996</v>
+        <v>0.77517100000000005</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0.16832800000000001</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" s="2">
-        <v>0.85012100000000002</v>
+        <v>0.86150300000000002</v>
       </c>
       <c r="C12" s="2">
-        <v>0.70994800000000002</v>
+        <v>0.709758</v>
       </c>
       <c r="D12" s="2">
         <v>0.86239900000000003</v>
       </c>
       <c r="E12" s="2">
-        <v>0.79986299999999999</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0.92438399999999998</v>
-      </c>
-      <c r="G12" s="4">
-        <v>0.93330500000000005</v>
+        <v>0.83274300000000001</v>
+      </c>
+      <c r="F12" s="4">
+        <v>0.92388700000000001</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0.93280600000000002</v>
       </c>
     </row>
   </sheetData>
